--- a/data/raw/inventory/Week 34/Tonor/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 34/Tonor/Seller FBA Inventory (SP-API).xlsx
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F10" t="n">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -1031,10 +1031,10 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>

--- a/data/raw/inventory/Week 34/Tonor/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 34/Tonor/Seller FBA Inventory (SP-API).xlsx
@@ -1949,7 +1949,7 @@
         <v>26</v>
       </c>
       <c r="F25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1961,7 +1961,7 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>26</v>
